--- a/Processed_Data/Mort_costs_check.xlsx
+++ b/Processed_Data/Mort_costs_check.xlsx
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Russia European part</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Russia European part</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">

--- a/Processed_Data/Mort_costs_check.xlsx
+++ b/Processed_Data/Mort_costs_check.xlsx
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Russia European part</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Russia European part</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
